--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdPartner001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdPartner001.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25330"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhouqiang\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65BFB0D2-7E08-4AB7-8146-20EECBDEE123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="21795" windowHeight="13245"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,20 +29,98 @@
     <t>合作机构*</t>
   </si>
   <si>
-    <t>生效日（yyyy-mm-dd）*</t>
+    <r>
+      <t>生效日（yyyy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dd）*</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>生效截止日期（yyyy-mm-dd）*</t>
+    <r>
+      <t>生效截止日期（yyyy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dd）*</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,13 +187,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -422,35 +499,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="10.9296875" customWidth="1"/>
+    <col min="1" max="1" width="10.875" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="22.59765625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="39.33203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="22.625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="39.375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -460,9 +537,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -471,9 +548,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdPartner001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdPartner001.xlsx
@@ -36,6 +36,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -45,6 +46,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -54,6 +56,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -63,12 +66,13 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>dd）*</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -78,6 +82,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -87,6 +92,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -96,6 +102,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -105,22 +112,20 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>dd）*</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
-  </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,18 +136,14 @@
     <font>
       <sz val="11"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -184,16 +185,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -505,8 +506,8 @@
   <cols>
     <col min="1" max="1" width="10.875" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="22.625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="39.375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="22.625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="39.375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -516,10 +517,10 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -530,7 +531,7 @@
       <c r="D2" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -541,7 +542,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -552,7 +553,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdPartner001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdPartner001.xlsx
@@ -26,9 +26,6 @@
     <t>产品主代码*</t>
   </si>
   <si>
-    <t>合作机构*</t>
-  </si>
-  <si>
     <r>
       <t>生效日（yyyy</t>
     </r>
@@ -118,6 +115,10 @@
       </rPr>
       <t>dd）*</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>合作机构（机构名称以“、”隔开）*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -505,7 +506,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10.875" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="2" max="2" width="31.875" customWidth="1"/>
     <col min="3" max="3" width="22.625" style="5" customWidth="1"/>
     <col min="4" max="4" width="39.375" style="5" customWidth="1"/>
   </cols>
@@ -515,13 +516,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4">
